--- a/维度得分.xlsx
+++ b/维度得分.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10668" windowHeight="3407"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="分数总览图" sheetId="1" r:id="rId1"/>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>9</v>
+        <v>8.41</v>
       </c>
       <c r="C4">
         <v>8.54</v>
@@ -1232,7 +1232,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2">
-        <v>8.41</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>5.55</v>
